--- a/data/trans_orig/Q25B01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q25B01-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de cigarrillos que fumaban antes de haber dejado de fumar</t>
+          <t>Número medio de cigarrillos que fumaban antes de haber dejado de fumar (tasa de respuesta: 96,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,01; 30,43</t>
+          <t>22,8; 30,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 27,19</t>
+          <t>17,42; 27,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,72; 23,58</t>
+          <t>16,64; 23,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,02; 32,6</t>
+          <t>23,22; 32,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,93</t>
+          <t>8,4; 14,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 17,23</t>
+          <t>9,61; 17,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 15,98</t>
+          <t>10,14; 15,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,95; 19,61</t>
+          <t>12,04; 19,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,08; 25,83</t>
+          <t>19,21; 25,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,73; 22,27</t>
+          <t>15,86; 22,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 19,59</t>
+          <t>14,77; 19,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,7; 29,32</t>
+          <t>21,46; 29,68</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,53; 24,26</t>
+          <t>19,52; 24,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,81; 26,66</t>
+          <t>20,64; 26,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,12; 29,82</t>
+          <t>22,83; 29,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,85; 21,34</t>
+          <t>15,62; 21,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 16,83</t>
+          <t>10,57; 17,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,84; 18,51</t>
+          <t>10,72; 18,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,37; 17,42</t>
+          <t>10,64; 17,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 12,95</t>
+          <t>9,04; 12,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,97; 22,3</t>
+          <t>18,05; 22,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,75; 22,23</t>
+          <t>17,56; 22,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,75; 25,23</t>
+          <t>19,45; 24,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,77; 17,75</t>
+          <t>13,79; 17,75</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,96; 26,25</t>
+          <t>19,1; 26,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,75; 28,05</t>
+          <t>21,65; 27,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,62; 21,77</t>
+          <t>16,7; 21,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,03; 22,19</t>
+          <t>17,07; 22,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 17,97</t>
+          <t>8,84; 17,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 21,99</t>
+          <t>11,76; 22,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,97; 13,0</t>
+          <t>9,04; 13,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 13,92</t>
+          <t>9,38; 14,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,48; 24,26</t>
+          <t>17,77; 23,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,81; 25,24</t>
+          <t>19,55; 24,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 18,34</t>
+          <t>14,72; 18,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,49; 18,34</t>
+          <t>14,35; 18,22</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,78; 24,46</t>
+          <t>19,92; 24,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,45; 27,12</t>
+          <t>20,47; 27,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,92; 26,02</t>
+          <t>19,09; 26,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,23; 22,67</t>
+          <t>17,15; 22,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 19,19</t>
+          <t>12,07; 19,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,16; 16,78</t>
+          <t>10,92; 17,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,92; 16,58</t>
+          <t>9,83; 16,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,13; 13,47</t>
+          <t>9,93; 13,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,67; 21,85</t>
+          <t>17,66; 21,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 23,34</t>
+          <t>18,25; 23,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,56; 22,15</t>
+          <t>16,59; 21,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,9; 18,79</t>
+          <t>14,85; 18,81</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,35; 27,13</t>
+          <t>17,98; 27,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,51; 30,97</t>
+          <t>20,55; 30,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,17; 31,47</t>
+          <t>21,12; 31,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,08; 34,27</t>
+          <t>18,04; 35,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 14,51</t>
+          <t>7,97; 14,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 16,22</t>
+          <t>9,04; 16,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 17,25</t>
+          <t>11,43; 17,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 15,8</t>
+          <t>11,1; 15,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,48; 20,65</t>
+          <t>14,47; 20,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,99; 25,28</t>
+          <t>16,88; 25,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,36; 26,28</t>
+          <t>18,87; 26,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 27,55</t>
+          <t>16,28; 27,99</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,11; 26,67</t>
+          <t>20,36; 26,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,32; 24,98</t>
+          <t>20,36; 24,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,82; 25,67</t>
+          <t>17,19; 25,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,23; 28,82</t>
+          <t>21,3; 29,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,57; 18,58</t>
+          <t>10,54; 18,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,49; 16,85</t>
+          <t>10,82; 16,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,56</t>
+          <t>6,67; 12,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,54; 17,59</t>
+          <t>10,42; 17,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,0; 24,01</t>
+          <t>18,2; 24,04</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,7; 22,8</t>
+          <t>18,69; 22,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,16; 21,96</t>
+          <t>15,13; 21,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,86; 26,06</t>
+          <t>19,46; 26,17</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,54; 26,29</t>
+          <t>21,4; 26,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,59; 26,65</t>
+          <t>21,83; 27,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,28; 23,24</t>
+          <t>18,21; 23,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,87; 21,5</t>
+          <t>17,04; 21,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,14; 19,65</t>
+          <t>12,32; 19,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,0; 15,32</t>
+          <t>11,96; 15,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,73; 16,48</t>
+          <t>12,69; 16,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,31; 13,77</t>
+          <t>10,12; 13,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,53; 23,83</t>
+          <t>19,33; 23,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,78; 22,49</t>
+          <t>18,69; 22,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,4; 20,2</t>
+          <t>16,65; 20,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,4; 17,54</t>
+          <t>14,27; 17,58</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,74; 23,35</t>
+          <t>18,65; 22,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,08; 24,89</t>
+          <t>18,87; 24,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,74; 23,92</t>
+          <t>18,7; 24,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,62; 21,41</t>
+          <t>19,5; 21,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,42; 12,98</t>
+          <t>9,39; 13,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,72; 14,85</t>
+          <t>10,86; 14,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,22; 17,35</t>
+          <t>12,14; 17,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,06; 19,13</t>
+          <t>14,06; 19,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,66; 19,22</t>
+          <t>15,75; 19,2</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,81; 20,98</t>
+          <t>16,75; 20,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,7; 20,68</t>
+          <t>16,61; 20,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,98; 20,86</t>
+          <t>19,0; 20,72</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21,4; 23,44</t>
+          <t>21,36; 23,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22,11; 24,47</t>
+          <t>22,08; 24,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20,54; 22,83</t>
+          <t>20,51; 22,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,74; 21,45</t>
+          <t>19,77; 21,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,83</t>
+          <t>11,64; 13,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,62</t>
+          <t>12,44; 14,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,4</t>
+          <t>12,41; 14,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,47; 13,11</t>
+          <t>11,39; 13,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,72; 20,4</t>
+          <t>18,81; 20,59</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,22; 21,0</t>
+          <t>19,14; 20,9</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,81; 19,62</t>
+          <t>17,66; 19,54</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,36; 19,18</t>
+          <t>17,36; 19,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25B01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q25B01-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,72</t>
+          <t>27,88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,26</t>
+          <t>16,44</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,13</t>
+          <t>25,56</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,8; 30,46</t>
+          <t>23,39; 30,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,42; 27,0</t>
+          <t>17,77; 27,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,64; 23,37</t>
+          <t>16,49; 23,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,22; 32,78</t>
+          <t>23,62; 32,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 14,78</t>
+          <t>8,45; 15,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 17,4</t>
+          <t>9,09; 16,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 15,97</t>
+          <t>10,33; 15,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,04; 19,71</t>
+          <t>12,6; 22,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,21; 25,76</t>
+          <t>19,03; 25,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,86; 22,88</t>
+          <t>16,06; 23,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,77; 19,82</t>
+          <t>14,46; 19,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,46; 29,68</t>
+          <t>22,14; 29,44</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,39</t>
+          <t>18,15</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,83</t>
+          <t>10,79</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,55</t>
+          <t>15,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,52; 24,4</t>
+          <t>19,28; 23,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,64; 26,14</t>
+          <t>20,58; 26,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,83; 29,73</t>
+          <t>23,14; 30,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,62; 21,07</t>
+          <t>15,59; 20,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 17,01</t>
+          <t>10,72; 16,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 18,04</t>
+          <t>10,78; 18,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 17,36</t>
+          <t>10,75; 17,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,04; 12,93</t>
+          <t>9,1; 12,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,05; 22,52</t>
+          <t>18,11; 22,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 22,16</t>
+          <t>17,63; 22,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,45; 24,96</t>
+          <t>19,77; 25,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,79; 17,75</t>
+          <t>13,72; 17,27</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,57</t>
+          <t>19,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,64</t>
+          <t>12,62</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,22</t>
+          <t>16,64</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,1; 26,53</t>
+          <t>19,01; 26,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,65; 27,63</t>
+          <t>21,63; 27,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,7; 21,64</t>
+          <t>16,65; 21,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,07; 22,37</t>
+          <t>17,13; 22,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,84; 17,64</t>
+          <t>8,83; 17,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,76; 22,18</t>
+          <t>11,7; 22,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,27</t>
+          <t>8,94; 13,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,38; 14,09</t>
+          <t>10,7; 15,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,77; 23,91</t>
+          <t>17,21; 23,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,55; 24,98</t>
+          <t>19,43; 24,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,72; 18,68</t>
+          <t>14,65; 18,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,35; 18,22</t>
+          <t>14,9; 18,62</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,81</t>
+          <t>19,91</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,62</t>
+          <t>11,18</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,69</t>
+          <t>16,62</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,92; 24,62</t>
+          <t>19,68; 24,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,47; 27,13</t>
+          <t>20,41; 27,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,09; 26,39</t>
+          <t>18,93; 26,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,15; 22,82</t>
+          <t>17,36; 22,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,07; 19,13</t>
+          <t>12,13; 19,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,92; 17,05</t>
+          <t>10,9; 16,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 16,62</t>
+          <t>10,26; 16,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 13,45</t>
+          <t>9,45; 13,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,66; 21,79</t>
+          <t>17,79; 21,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,25; 23,51</t>
+          <t>18,27; 23,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 21,91</t>
+          <t>16,34; 21,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,85; 18,81</t>
+          <t>14,9; 18,62</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,64</t>
+          <t>24,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,07</t>
+          <t>13,02</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,48</t>
+          <t>20,47</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,98; 27,22</t>
+          <t>18,3; 27,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,55; 30,98</t>
+          <t>20,42; 30,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,12; 31,28</t>
+          <t>21,42; 31,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,04; 35,21</t>
+          <t>18,05; 35,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 14,53</t>
+          <t>7,98; 14,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 16,2</t>
+          <t>9,06; 16,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,43; 17,13</t>
+          <t>11,21; 16,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,1; 15,54</t>
+          <t>11,22; 15,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,47; 20,86</t>
+          <t>14,51; 20,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,88; 25,53</t>
+          <t>17,21; 25,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,87; 26,2</t>
+          <t>18,45; 26,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,28; 27,99</t>
+          <t>16,41; 27,79</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,23</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,13</t>
+          <t>12,92</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,86</t>
+          <t>22,84</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,36; 26,86</t>
+          <t>19,89; 27,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,36; 24,9</t>
+          <t>20,37; 24,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,19; 25,51</t>
+          <t>17,3; 25,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,3; 29,1</t>
+          <t>21,84; 29,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,54; 18,74</t>
+          <t>10,75; 18,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,82; 16,77</t>
+          <t>10,88; 16,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,71</t>
+          <t>6,93; 13,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,42; 17,24</t>
+          <t>10,45; 17,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,2; 24,04</t>
+          <t>18,13; 24,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,69; 22,87</t>
+          <t>18,87; 23,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,13; 21,87</t>
+          <t>15,05; 21,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,46; 26,17</t>
+          <t>20,18; 26,41</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>18,75</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,77</t>
+          <t>11,82</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,96</t>
+          <t>15,78</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,4; 26,35</t>
+          <t>21,34; 26,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,83; 27,08</t>
+          <t>21,84; 26,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,21; 23,51</t>
+          <t>18,28; 23,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,04; 21,63</t>
+          <t>16,58; 21,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,32; 19,99</t>
+          <t>12,23; 19,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,96; 15,25</t>
+          <t>12,02; 15,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,69; 16,5</t>
+          <t>12,56; 16,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,12; 13,43</t>
+          <t>10,26; 13,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,33; 23,72</t>
+          <t>19,47; 23,86</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,69; 22,39</t>
+          <t>18,74; 22,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,65; 20,19</t>
+          <t>16,64; 20,11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,27; 17,58</t>
+          <t>14,19; 17,37</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20,26</t>
+          <t>20,85</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16,33</t>
+          <t>15,86</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19,88</t>
+          <t>19,47</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,65; 22,99</t>
+          <t>18,6; 23,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,87; 24,71</t>
+          <t>19,09; 24,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,7; 24,21</t>
+          <t>18,71; 24,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,5; 21,38</t>
+          <t>19,76; 22,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,39; 13,01</t>
+          <t>9,41; 12,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,86; 14,85</t>
+          <t>10,78; 14,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1731,27 +1731,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,06; 19,0</t>
+          <t>13,44; 18,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,75; 19,2</t>
+          <t>15,54; 19,07</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,75; 20,95</t>
+          <t>16,75; 20,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,61; 20,82</t>
+          <t>16,65; 20,63</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,0; 20,72</t>
+          <t>18,3; 20,65</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20,51</t>
+          <t>20,56</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>12,34</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,17</t>
+          <t>17,63</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21,36; 23,45</t>
+          <t>21,37; 23,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22,08; 24,29</t>
+          <t>22,06; 24,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20,51; 22,81</t>
+          <t>20,49; 22,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,77; 21,55</t>
+          <t>19,54; 21,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,64; 13,87</t>
+          <t>11,5; 13,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,44; 14,52</t>
+          <t>12,42; 14,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,49</t>
+          <t>12,36; 14,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,39; 13,09</t>
+          <t>11,51; 13,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,81; 20,59</t>
+          <t>18,73; 20,44</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,14; 20,9</t>
+          <t>19,21; 21,02</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,66; 19,54</t>
+          <t>17,85; 19,52</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,36; 19,12</t>
+          <t>16,91; 18,44</t>
         </is>
       </c>
     </row>
